--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488238_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488238_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7368</v>
+        <v>4.471</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9385</v>
+        <v>8.4512</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.2017</v>
+        <v>-3.9801</v>
       </c>
       <c r="G2" t="n">
         <v>3.7855</v>
@@ -610,13 +610,13 @@
         <v>3.5205</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1953</v>
+        <v>-0.461</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7822</v>
+        <v>-0.2695</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4131</v>
+        <v>-0.1915</v>
       </c>
       <c r="V2" t="n">
         <v>1.8877</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3554</v>
+        <v>3.5753</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4215</v>
+        <v>2.7153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9339</v>
+        <v>0.86</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7357</v>
@@ -688,13 +688,13 @@
         <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0726</v>
+        <v>0.2925</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1641</v>
+        <v>0.1296</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2368</v>
+        <v>0.1629</v>
       </c>
       <c r="V3" t="n">
         <v>3.4627</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9535</v>
+        <v>-0.6838</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.211</v>
+        <v>-1.0152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2575</v>
+        <v>0.3314</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5554</v>
@@ -1000,13 +1000,13 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.713</v>
+        <v>-0.4433</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3071</v>
+        <v>-0.1113</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4059</v>
+        <v>-0.332</v>
       </c>
       <c r="V7" t="n">
         <v>0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8775</v>
+        <v>-2.9256</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6923</v>
+        <v>-1.8881</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1852</v>
+        <v>-1.0375</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3553</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0781</v>
+        <v>-0.1262</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3457</v>
+        <v>0.1499</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4238</v>
+        <v>-0.2761</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.508</v>
+        <v>-3.4856</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3931</v>
+        <v>-1.2722</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1149</v>
+        <v>-2.2134</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2035</v>
@@ -1156,13 +1156,13 @@
         <v>2.4087</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4151</v>
+        <v>-0.3926</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4539</v>
+        <v>-0.3329</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0388</v>
+        <v>-0.0597</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0011</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4259</v>
+        <v>-4.2844</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5894</v>
+        <v>-2.3435</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8365</v>
+        <v>-1.9408</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7393</v>
+        <v>-2.2052</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6215000000000001</v>
+        <v>-2.7443</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3608</v>
+        <v>0.5391</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3495</v>
+        <v>1.9365</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9194</v>
+        <v>-0.6146</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5699</v>
+        <v>2.5511</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0888</v>
+        <v>-4.1417</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.298</v>
+        <v>-2.1297</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-2.012</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.891</v>
+        <v>-2.594</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.6703</v>
+        <v>-4.8175</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5183</v>
+        <v>0.5148</v>
       </c>
       <c r="T10" t="n">
-        <v>0.102</v>
+        <v>-0.092</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4163</v>
+        <v>0.6068</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0.6294</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9433</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5771</v>
+        <v>-5.0655</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5624</v>
+        <v>-3.9581</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0147</v>
+        <v>-1.1073</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2052</v>
+        <v>-0.7393</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7443</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5391</v>
+        <v>-1.3608</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9365</v>
+        <v>2.3495</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6146</v>
+        <v>2.9194</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5511</v>
+        <v>-0.5699</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1417</v>
+        <v>-3.0888</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1297</v>
+        <v>-2.298</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.012</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.594</v>
+        <v>-3.891</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8175</v>
+        <v>-6.6703</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2221</v>
+        <v>-0.1212</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3109</v>
+        <v>-0.2667</v>
       </c>
       <c r="U11" t="n">
-        <v>0.533</v>
+        <v>0.1455</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
       <c r="W11" t="n">
         <v>0.6294</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6294</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7692</v>
+        <v>-5.8431</v>
       </c>
       <c r="E12" t="n">
         <v>-4.2345</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5348</v>
+        <v>-1.6086</v>
       </c>
       <c r="G12" t="n">
         <v>-6.3306</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1908</v>
+        <v>0.1169</v>
       </c>
       <c r="T12" t="n">
         <v>0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1186</v>
+        <v>0.0448</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.266</v>
+        <v>-5.9493</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8821</v>
+        <v>-2.5653</v>
       </c>
       <c r="F13" t="n">
         <v>-3.3839</v>
@@ -1468,10 +1468,10 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.623</v>
+        <v>-0.3062</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4539</v>
+        <v>-0.1371</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1691</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.9967</v>
+        <v>-18.9027</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.916499999999999</v>
+        <v>-4.822100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.0803</v>
+        <v>-14.0802</v>
       </c>
       <c r="G14" t="n">
         <v>-18.6942</v>
@@ -1546,13 +1546,13 @@
         <v>17.6022</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0207</v>
+        <v>-0.9263</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9523</v>
+        <v>-0.8578999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06839999999999992</v>
+        <v>-0.06839999999999991</v>
       </c>
       <c r="V14" t="n">
         <v>5.350399999999999</v>
@@ -1561,7 +1561,7 @@
         <v>9.4397</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.089300000000001</v>
+        <v>-4.0893</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2614</v>
+        <v>6.4246</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1855</v>
+        <v>4.0876</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0759</v>
+        <v>2.337</v>
       </c>
       <c r="G15" t="n">
         <v>7.843</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3581</v>
+        <v>-0.1949</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3544</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2617</v>
+        <v>5.7428</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0373</v>
+        <v>4.3311</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2244</v>
+        <v>1.4116</v>
       </c>
       <c r="G16" t="n">
         <v>4.7647</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.115</v>
+        <v>-0.6339</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4037</v>
+        <v>-0.2164</v>
       </c>
       <c r="V16" t="n">
         <v>0.315</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2673</v>
+        <v>3.7194</v>
       </c>
       <c r="E17" t="n">
-        <v>5.6027</v>
+        <v>1.7859</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3355</v>
+        <v>1.9335</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1978</v>
+        <v>2.1233</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5604</v>
+        <v>0.896</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6373</v>
+        <v>1.2273</v>
       </c>
       <c r="J17" t="n">
-        <v>5.613</v>
+        <v>2.573</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9067</v>
+        <v>1.868</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7063</v>
+        <v>0.705</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4152</v>
+        <v>-0.4497</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3463</v>
+        <v>-0.972</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.5223</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3431</v>
+        <v>0.48</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2137</v>
+        <v>0.1393</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1294</v>
+        <v>0.3407</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6441</v>
+        <v>0.1897</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.273</v>
+        <v>0.1897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2292</v>
+        <v>3.4833</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3941</v>
+        <v>4.9172</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8351</v>
+        <v>-1.4339</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1233</v>
+        <v>4.1978</v>
       </c>
       <c r="H18" t="n">
-        <v>0.896</v>
+        <v>1.5604</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2273</v>
+        <v>2.6373</v>
       </c>
       <c r="J18" t="n">
-        <v>2.573</v>
+        <v>5.613</v>
       </c>
       <c r="K18" t="n">
-        <v>1.868</v>
+        <v>2.9067</v>
       </c>
       <c r="L18" t="n">
-        <v>0.705</v>
+        <v>2.7063</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4497</v>
+        <v>-1.4152</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.972</v>
+        <v>-1.3463</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5223</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0102</v>
+        <v>1.5591</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2524</v>
+        <v>0.5282</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2422</v>
+        <v>1.0309</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1897</v>
+        <v>-2.6441</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1897</v>
+        <v>-3.273</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8562</v>
+        <v>2.7668</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1655</v>
+        <v>0.8717</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6907</v>
+        <v>1.8951</v>
       </c>
       <c r="G19" t="n">
         <v>3.1664</v>
@@ -1936,13 +1936,13 @@
         <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2244</v>
+        <v>1.135</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6703</v>
+        <v>0.3765</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5541</v>
+        <v>0.7585</v>
       </c>
       <c r="V19" t="n">
         <v>0.5034999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6585</v>
+        <v>1.1968</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9193</v>
+        <v>1.5069</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2608</v>
+        <v>-0.31</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4563</v>
@@ -2092,13 +2092,13 @@
         <v>2.4087</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0555</v>
+        <v>0.5938</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6901</v>
+        <v>-0.1026</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7456</v>
+        <v>0.6964</v>
       </c>
       <c r="V21" t="n">
         <v>0.5034999999999999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0486</v>
+        <v>0.2171</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5942</v>
+        <v>-1.2961</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6428</v>
+        <v>1.5132</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4081</v>
+        <v>-0.1945</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1126</v>
+        <v>-0.3435</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.149</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8853</v>
+        <v>-0.7489</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2064</v>
+        <v>-0.7904</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3211</v>
+        <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2934</v>
+        <v>0.5544</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0938</v>
+        <v>0.4469</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1996</v>
+        <v>0.1076</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.2263</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3209</v>
+        <v>0.3793</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1858</v>
+        <v>-0.153</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1351</v>
+        <v>-0.253</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2961</v>
+        <v>0.2025</v>
       </c>
       <c r="F23" t="n">
-        <v>1.161</v>
+        <v>-0.4555</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1945</v>
+        <v>-0.4081</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3435</v>
+        <v>0.1126</v>
       </c>
       <c r="I23" t="n">
-        <v>0.149</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7489</v>
+        <v>0.8853</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7904</v>
+        <v>1.2064</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0415</v>
+        <v>-0.3211</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5544</v>
+        <v>-1.2934</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4469</v>
+        <v>-1.0938</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1076</v>
+        <v>-0.1996</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1258</v>
+        <v>0.3022</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3793</v>
+        <v>-0.0709</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5051</v>
+        <v>0.373</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8262</v>
+        <v>-0.8428</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3742</v>
+        <v>-2.4721</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5479</v>
+        <v>1.6293</v>
       </c>
       <c r="G24" t="n">
         <v>-2.426</v>
@@ -2326,13 +2326,13 @@
         <v>3.5205</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0766</v>
+        <v>0.06</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4203</v>
+        <v>-0.5182</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4969</v>
+        <v>0.5782</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0708</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.816</v>
+        <v>-2.4409</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0659</v>
+        <v>-1.7721</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7501</v>
+        <v>-0.6687</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2043</v>
@@ -2404,13 +2404,13 @@
         <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5763</v>
+        <v>-0.2011</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4377</v>
+        <v>-0.1439</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1385</v>
+        <v>-0.0572</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5177</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19.9967</v>
+        <v>21.3024</v>
       </c>
       <c r="E26" t="n">
-        <v>13.4507</v>
+        <v>13.4509</v>
       </c>
       <c r="F26" t="n">
-        <v>6.5458</v>
+        <v>7.8516</v>
       </c>
       <c r="G26" t="n">
         <v>18.6943</v>
@@ -2482,13 +2482,13 @@
         <v>22.2344</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0208</v>
+        <v>3.3265</v>
       </c>
       <c r="T26" t="n">
-        <v>0.06869999999999987</v>
+        <v>0.06860000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9523</v>
+        <v>3.2578</v>
       </c>
       <c r="V26" t="n">
         <v>-5.3504</v>
